--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 06,08,26 млрсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 06,08,26 млрсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2744F6C-DB7E-4542-8A75-C19BC4FD0E7F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB4246B-E497-4A45-8681-B40F88EDCE86}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="174">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -587,6 +587,9 @@
   <si>
     <t>05,08,</t>
   </si>
+  <si>
+    <t>нет заказа</t>
+  </si>
 </sst>
 </file>
 
@@ -1358,7 +1361,9 @@
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="7"/>
-      <c r="AI4" s="9"/>
+      <c r="AI4" s="9" t="s">
+        <v>173</v>
+      </c>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
       <c r="AL4" s="1"/>
@@ -5492,7 +5497,7 @@
         <v>91</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L67" si="11">E38-K38</f>
         <v>0</v>
       </c>
       <c r="M38" s="1"/>
@@ -5511,7 +5516,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="1">
-        <f t="shared" ref="T38:T69" si="13">(F38+O38+S38)/Q38</f>
+        <f t="shared" ref="T38:T67" si="13">(F38+O38+S38)/Q38</f>
         <v>15.384615384615385</v>
       </c>
       <c r="U38" s="1">
@@ -5937,11 +5942,11 @@
         <v>10</v>
       </c>
       <c r="AI41" s="9">
-        <f t="shared" ref="AI41:AI72" si="17">MROUND(R41, AH41*AK41)/AH41</f>
+        <f t="shared" ref="AI41:AI66" si="17">MROUND(R41, AH41*AK41)/AH41</f>
         <v>0</v>
       </c>
       <c r="AJ41" s="1">
-        <f t="shared" ref="AJ41:AJ72" si="18">AI41*AH41*G41</f>
+        <f t="shared" ref="AJ41:AJ66" si="18">AI41*AH41*G41</f>
         <v>0</v>
       </c>
       <c r="AK41" s="1">
@@ -5951,7 +5956,7 @@
         <v>84</v>
       </c>
       <c r="AM41" s="9">
-        <f t="shared" ref="AM41:AM72" si="19">AI41/AL41</f>
+        <f t="shared" ref="AM41:AM66" si="19">AI41/AL41</f>
         <v>0</v>
       </c>
       <c r="AN41" s="1"/>
